--- a/verification/cases/roundtrip/drawing/init.xlsx
+++ b/verification/cases/roundtrip/drawing/init.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{122F6B72-0942-4007-8574-237D71763B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,8 +17,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -54,6 +55,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -74,7 +83,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="clock.jpg"/>
+        <xdr:cNvPr id="2" name="Picture 1" descr="clock.jpg">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -112,7 +127,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2" descr="cow.pict"/>
+        <xdr:cNvPr id="3" name="Picture 2" descr="cow.pict">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -150,7 +171,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4" descr="tomcat.png"/>
+        <xdr:cNvPr id="5" name="Picture 4" descr="tomcat.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -188,7 +215,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 6" descr="wrench.emf"/>
+        <xdr:cNvPr id="7" name="Picture 6" descr="wrench.emf">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -221,7 +254,13 @@
     <xdr:ext cx="1905971" cy="436786"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="TextBox 8"/>
+        <xdr:cNvPr id="9" name="TextBox 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -301,7 +340,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 7" descr="santa.wmf"/>
+        <xdr:cNvPr id="8" name="Picture 7" descr="santa.wmf">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -328,9 +373,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -368,7 +413,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -402,6 +447,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -436,9 +482,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -611,9 +658,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -621,18 +668,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
